--- a/docs/StructureDefinition-videre-forlop-extension.xlsx
+++ b/docs/StructureDefinition-videre-forlop-extension.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Neste skritt i forløpet.</t>
+    <t>Next Step</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-08T17:39:22+01:00</t>
+    <t>2025-11-11T17:38:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Angir videre forløp</t>
+    <t>Next step in the grading process after photography. (4000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-videre-forlop-extension.xlsx
+++ b/docs/StructureDefinition-videre-forlop-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-12T18:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-videre-forlop-extension.xlsx
+++ b/docs/StructureDefinition-videre-forlop-extension.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Next Step</t>
+    <t>Grading Pending</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:21:01+01:00</t>
+    <t>2025-11-13T17:39:30+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-videre-forlop-extension.xlsx
+++ b/docs/StructureDefinition-videre-forlop-extension.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Next Step</t>
+    <t>Grading Pending</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-15T17:14:08+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Next step in the grading process after photography. (4000-series)</t>
+    <t>Next step in grading this examination. (4000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-videre-forlop-extension.xlsx
+++ b/docs/StructureDefinition-videre-forlop-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-15T17:14:08+01:00</t>
+    <t>2025-11-16T16:39:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
